--- a/archive/2026/2026-10-22.xlsx
+++ b/archive/2026/2026-10-22.xlsx
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-2186</v>
+        <v>-2185</v>
       </c>
       <c r="L10" t="n">
         <v>414</v>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E15" t="n">
         <v>2385</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="E18" t="n">
         <v>986</v>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1065</v>
+        <v>-1015</v>
       </c>
       <c r="L20" t="n">
-        <v>1840</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>-40</v>
+        <v>42.35</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="21">
@@ -7438,22 +7438,22 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1015</v>
+        <v>-944</v>
       </c>
       <c r="L21" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>1.05</v>
+        <v>1840</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>-40</v>
       </c>
     </row>
     <row r="22">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="E28" t="n">
         <v>1115</v>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-537</v>
+        <v>-539</v>
       </c>
       <c r="L28" t="n">
         <v>260</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>-399</v>
+        <v>-390</v>
       </c>
       <c r="L35" t="n">
         <v>40</v>
@@ -8106,22 +8106,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E36" t="n">
-        <v>480.5</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>0.5</v>
+        <v>1560</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>-100</v>
       </c>
       <c r="H36" t="n">
         <v>33</v>
@@ -8152,22 +8152,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E37" t="n">
-        <v>29.6</v>
+        <v>480.5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
         <v>34</v>
@@ -8198,22 +8198,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="E38" t="n">
-        <v>1265</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>-75</v>
+        <v>29.6</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
         <v>35</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="E39" t="n">
-        <v>95.90000000000001</v>
+        <v>846</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-6.6</v>
+        <v>-31</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
@@ -8290,22 +8290,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="E40" t="n">
-        <v>114.5</v>
+        <v>1265</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-0.5</v>
+        <v>-75</v>
       </c>
       <c r="H40" t="n">
         <v>37</v>
@@ -8336,22 +8336,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="E41" t="n">
-        <v>3145</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-90</v>
+        <v>-6.6</v>
       </c>
       <c r="H41" t="n">
         <v>38</v>
@@ -8382,22 +8382,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="E42" t="n">
-        <v>5275</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>145</v>
+        <v>114.5</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>-0.5</v>
       </c>
       <c r="H42" t="n">
         <v>39</v>
@@ -8428,22 +8428,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E43" t="n">
-        <v>113.5</v>
+        <v>3145</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-0.5</v>
+        <v>-90</v>
       </c>
       <c r="H43" t="n">
         <v>40</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E44" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>-0.1</v>
+        <v>5275</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>145</v>
       </c>
       <c r="H44" t="n">
         <v>41</v>
@@ -8520,22 +8520,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="E45" t="n">
-        <v>479</v>
+        <v>113.5</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-27</v>
+        <v>-0.5</v>
       </c>
       <c r="H45" t="n">
         <v>42</v>
@@ -8566,22 +8566,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>允強</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E46" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0.35</v>
+        <v>67.8</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>-0.1</v>
       </c>
       <c r="H46" t="n">
         <v>43</v>
@@ -8612,44 +8612,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>和益</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E47" t="n">
-        <v>55.3</v>
+        <v>479</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-0.7</v>
+        <v>-27</v>
       </c>
       <c r="H47" t="n">
         <v>44</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="L47" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="M47" s="6" t="n">
-        <v>1</v>
+        <v>6070</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>-465</v>
       </c>
     </row>
     <row r="48">
@@ -8658,44 +8658,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>允強</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E48" t="n">
-        <v>16.95</v>
+        <v>24.35</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="H48" t="n">
         <v>45</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="K48" s="7" t="n">
-        <v>-181</v>
+        <v>-189</v>
       </c>
       <c r="L48" t="n">
-        <v>248</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <v>-18</v>
+        <v>196.5</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -8704,44 +8704,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>和益</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E49" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>0.15</v>
+        <v>55.3</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>-0.7</v>
       </c>
       <c r="H49" t="n">
         <v>46</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>國碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>-172</v>
+        <v>-181</v>
       </c>
       <c r="L49" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>0.6</v>
+        <v>248</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="50">
@@ -8750,44 +8750,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E50" t="n">
-        <v>1560</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>-100</v>
+        <v>16.95</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0.05</v>
       </c>
       <c r="H50" t="n">
         <v>47</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>國碩</t>
         </is>
       </c>
       <c r="K50" s="7" t="n">
-        <v>-164</v>
+        <v>-172</v>
       </c>
       <c r="L50" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>-0.8</v>
+        <v>30.5</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="51">
@@ -8796,44 +8796,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E51" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="F51" s="8" t="n">
-        <v>-0.75</v>
+        <v>20.5</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0.15</v>
       </c>
       <c r="H51" t="n">
         <v>48</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-145</v>
+        <v>-164</v>
       </c>
       <c r="L51" t="n">
-        <v>6070</v>
+        <v>80.5</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>-465</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="52">
@@ -8842,22 +8842,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E52" t="n">
-        <v>597</v>
+        <v>56.3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-18</v>
+        <v>-0.75</v>
       </c>
       <c r="H52" t="n">
         <v>49</v>
@@ -8888,22 +8888,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E53" t="n">
-        <v>567</v>
+        <v>224.5</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="H53" t="n">
         <v>50</v>

--- a/archive/2026/2026-10-22.xlsx
+++ b/archive/2026/2026-10-22.xlsx
@@ -14,11 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_外資_上櫃" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_投信_上櫃" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_自營商_上櫃" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_外資_上市" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_投信_上市" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_自營商_上市" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_三大法人合計_上市" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2875,3654 +2871,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市自營商買賣超排行｜2026-10-22｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>13361</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-619683</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>9005</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-186856</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>8615</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-102520</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>6737</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-93165</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>6442</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-68401</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>4909</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-65923</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4725</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>00415A</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>主動群益核心50</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-45698</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4581</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-44519</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4535</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-42885</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4030</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-38780</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>3854</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-27417</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3791</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-25538</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3789</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-22979</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3782</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-19998</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>3523</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-19525</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>3212</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-19332</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>3084</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-17971</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>主動元大AI新經濟</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>2896</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00665L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>富邦恒生國企正2</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-13638</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2653</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-12198</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>2447</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-12195</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>2391</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-12125</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2269</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-10744</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00885</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>富邦越南</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1935</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-9471</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1890</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-9453</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>009820</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>元大納斯達克精選</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1877</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-8823</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1533</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-7482</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1335</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-7341</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>009821</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>野村稀土關鍵資源</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1315</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-7128</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1287</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-7011</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1196</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-4998</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-4496</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>009805</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>台新美國電力基建</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1047</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>00671R</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ反1</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-4424</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1010</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-4420</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>00669R</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>國泰美國道瓊反1</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>932</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>00650L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>復華香港正2</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-4232</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>892</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>00410A</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>主動永豐科技趨勢</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-3706</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00651R</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>復華香港反1</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>850</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-3695</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>830</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>00951</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>台新日本半導體</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-3074</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>825</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>009803</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>玉山市值動能50</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-3037</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>824</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00954</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>中信日本半導體</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-2881</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>00715L</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>期街口布蘭特正2</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>810</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-2873</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>790</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>009827</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>玉山未來全球算力</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-2751</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>誠美材</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>746</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-2703</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>742</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00662</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-2662</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>741</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00999A</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>主動野村臺灣高息</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-2593</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>00713</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>元大台灣高息低波</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>736</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>台新AI優息動能</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-2591</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>721</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>00404A</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>主動聯博動能50</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-2402</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>00983D</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>主動富邦複合收益</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>698</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>00401A</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>主動摩根台灣鑫收</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-2389</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00915</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>凱基優選高股息30</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>698</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-2265</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>671</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>00882</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>中信中國高股息</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1997</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>650</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00408A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>主動第一金優股息</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-1946</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市三大法人合計買賣超排行｜2026-10-22｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>33359</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-742044</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>28524</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-195571</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>24928</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-102610</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>14859</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-100841</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>14023</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-98528</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>11063</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-94548</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>10693</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-82663</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>10437</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-69135</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>東台</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>10370</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-46603</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>10314</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-46513</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>10161</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00415A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動群益核心50</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-43650</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>9679</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-38294</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>9367</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-32888</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>9344</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-32586</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>9218</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-28501</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>9103</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-27922</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>9044</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-25514</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>8971</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-24261</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>8788</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-22969</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>8652</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-21637</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>8444</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-21427</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>7942</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-20713</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>6532</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-16585</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>6287</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-16261</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>6275</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-16156</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>6080</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-13762</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>5861</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-13260</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>5716</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00665L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>富邦恒生國企正2</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-12550</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>5679</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-11872</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>5202</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-11526</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>5077</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-11219</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>台中銀</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>4969</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>瑞軒</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-10278</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>4881</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-10149</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>4852</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-9709</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>4639</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>中石化</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-9434</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>4398</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-9207</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>4330</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-9020</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>廣宇</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>4269</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-8677</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>4227</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-8423</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>4024</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-7553</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>4018</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6209</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-6548</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>3833</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-6340</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>3747</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-6205</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>3732</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-5798</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>3676</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-5575</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>3405</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-5425</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>主動元大AI新經濟</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>3362</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-5019</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>3354</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-4628</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>3316</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>00650L</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>復華香港正2</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-4503</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>麗臺</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>3195</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-4480</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19733,3613 +16081,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市外資買賣超排行｜2026-10-22｜單位：張</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>25549</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-122362</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>25236</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-56720</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>24665</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-45990</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>12843</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-41971</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>12635</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-34918</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>10912</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-20416</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>東台</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>9978</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-18768</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>9936</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-16066</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>9327</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-15756</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>9221</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-14616</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-12814</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>7743</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-12695</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>7699</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-12225</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>7580</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-10851</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>7119</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-10106</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>7009</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>瑞軒</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-9616</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>6377</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>中石化</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-9371</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>6059</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-9347</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>6009</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-9232</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>5819</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-8876</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>5578</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-8714</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>5442</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-6254</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>5422</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-6181</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>5072</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-6071</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>台中銀</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>4964</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-6060</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4952</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6209</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-6039</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>4639</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-5512</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>4576</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-5438</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>4523</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-5230</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>4521</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-5224</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>4505</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-5007</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>4503</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-4943</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>4480</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-4437</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>廣宇</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>4439</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6443</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>元晶</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-4377</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>4110</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-4356</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>3910</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-4262</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>3858</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-4247</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>3718</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-4044</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>3556</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-3994</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>3506</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>中工</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-3956</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>麗臺</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>3143</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-3329</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>中環</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>2972</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-3208</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>2725</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-2982</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>2662</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-2963</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>潤泰新</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>2613</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-2950</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>佳世達</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>2582</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>長興</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-2816</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>遠東銀</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>2425</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-2619</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>4989</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>榮科</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>2324</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-2581</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>萬海</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2304</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-2421</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>2278</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-2410</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市投信買賣超排行｜2026-10-22｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>4839</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-8806</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>4726</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-8119</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>2968</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-4775</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>2251</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-4176</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>2106</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-3268</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-2537</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>1976</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-2185</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>遠東新</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1763</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-1877</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>1618</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-1776</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1453</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-1773</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>1415</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-1471</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-1358</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1098</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-1297</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1077</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-1208</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1073</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-1100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1049</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-1083</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>832</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-1015</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>816</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-944</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>650</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-882</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-826</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-802</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>547</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-740</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>546</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>致伸</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-736</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>521</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-588</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>498</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-539</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>495</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-515</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>日電貿</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>461</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-504</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>440</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-475</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>404</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>和桐</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-460</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>395</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-411</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-409</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>357</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-390</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>341</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-322</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>6715</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>嘉基</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>324</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>漢翔</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-317</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>潤泰新</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>314</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-307</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>309</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00850</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>元大臺灣ESG永續</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>裕民</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-293</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-284</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>230</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>群光</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-270</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>212</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-256</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>196</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-223</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-192</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2393</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>億光</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>185</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-191</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>尖點</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>182</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-190</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>176</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>可成</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-189</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-181</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>和益</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>國碩</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-172</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-164</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-137</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-136</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
+        </is>
       </c>
     </row>
   </sheetData>
